--- a/指标样例表.xlsx
+++ b/指标样例表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\研究生\实习\毕马威实习\财险年报平台\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F44207E-AA60-4A1A-B301-EF0288B58864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D04388-FEBC-47A3-8F0D-77000FBE21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="104">
   <si>
     <t>类别</t>
   </si>
@@ -335,6 +335,14 @@
   </si>
   <si>
     <t>[投资成分]/[保险业务收入]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024YE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025YE</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -726,14 +734,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,14 +751,20 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -760,11 +774,11 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -774,11 +788,11 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -788,11 +802,11 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -802,14 +816,14 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>97</v>
       </c>
@@ -819,11 +833,11 @@
       <c r="C6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -833,14 +847,14 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -850,11 +864,11 @@
       <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -864,11 +878,11 @@
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -878,11 +892,11 @@
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -892,11 +906,11 @@
       <c r="C11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -906,14 +920,14 @@
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -923,11 +937,11 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -937,11 +951,11 @@
       <c r="C14" t="s">
         <v>7</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -951,11 +965,11 @@
       <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -965,14 +979,14 @@
       <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -982,11 +996,11 @@
       <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -996,11 +1010,11 @@
       <c r="C18" t="s">
         <v>7</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1010,14 +1024,14 @@
       <c r="C19" t="s">
         <v>20</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>66</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -1027,11 +1041,11 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1041,11 +1055,11 @@
       <c r="C21" t="s">
         <v>7</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1055,11 +1069,11 @@
       <c r="C22" t="s">
         <v>7</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1069,11 +1083,11 @@
       <c r="C23" t="s">
         <v>7</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1083,14 +1097,14 @@
       <c r="C24" t="s">
         <v>20</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>71</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -1100,14 +1114,14 @@
       <c r="C25" t="s">
         <v>20</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>72</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1117,14 +1131,14 @@
       <c r="C26" t="s">
         <v>20</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>73</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1134,11 +1148,11 @@
       <c r="C27" t="s">
         <v>7</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1148,11 +1162,11 @@
       <c r="C28" t="s">
         <v>7</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1162,14 +1176,14 @@
       <c r="C29" t="s">
         <v>20</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>76</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1179,11 +1193,11 @@
       <c r="C30" t="s">
         <v>7</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1193,11 +1207,11 @@
       <c r="C31" t="s">
         <v>7</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1207,14 +1221,14 @@
       <c r="C32" t="s">
         <v>20</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>79</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1224,11 +1238,11 @@
       <c r="C33" t="s">
         <v>7</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1238,11 +1252,11 @@
       <c r="C34" t="s">
         <v>7</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1252,11 +1266,11 @@
       <c r="C35" t="s">
         <v>7</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1266,11 +1280,11 @@
       <c r="C36" t="s">
         <v>7</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1280,11 +1294,11 @@
       <c r="C37" t="s">
         <v>7</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1294,11 +1308,11 @@
       <c r="C38" t="s">
         <v>7</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -1308,11 +1322,11 @@
       <c r="C39" t="s">
         <v>7</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -1322,7 +1336,7 @@
       <c r="C40" t="s">
         <v>7</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>87</v>
       </c>
     </row>

--- a/指标样例表.xlsx
+++ b/指标样例表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\研究生\实习\毕马威实习\财险年报平台\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D04388-FEBC-47A3-8F0D-77000FBE21BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3955A05D-BC7E-49AA-AF49-63C62354E0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$I$40</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="106">
   <si>
     <t>类别</t>
   </si>
@@ -343,6 +343,14 @@
   </si>
   <si>
     <t>2025YE</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -734,614 +742,620 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>54</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>59</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>20</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>63</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>66</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>31</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
         <v>14</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>20</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>71</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>20</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>72</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
         <v>14</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>20</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>73</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
         <v>15</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>39</v>
       </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
         <v>15</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>40</v>
       </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
         <v>41</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>20</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>76</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
         <v>42</v>
       </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
         <v>43</v>
       </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D32" t="s">
         <v>44</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>20</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>79</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>5</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>8</v>
       </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>5</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>5</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>5</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
         <v>45</v>
       </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>46</v>
       </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
         <v>16</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38" t="s">
         <v>47</v>
       </c>
-      <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
         <v>16</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
         <v>48</v>
       </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
         <v>16</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
         <v>49</v>
       </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C1:G40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/指标样例表.xlsx
+++ b/指标样例表.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$H$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="198">
   <si>
     <t>公司类型</t>
   </si>
@@ -54,6 +54,9 @@
     <t>字段类型</t>
   </si>
   <si>
+    <t>2023YE</t>
+  </si>
+  <si>
     <t>2024YE</t>
   </si>
   <si>
@@ -90,7 +93,7 @@
     <t>计算</t>
   </si>
   <si>
-    <t>（1-[综合成本率]）*[保险服务收入]</t>
+    <t>（1-[综合成本率]）×[保险服务收入]</t>
   </si>
   <si>
     <t>投资利润</t>
@@ -144,7 +147,7 @@
     <t>平安产险的“保险产品经营信息”表格中，“农业保险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-货运保险</t>
+    <t>保险服务收入-货物运输险</t>
   </si>
   <si>
     <t>平安产险的“保险产品经营信息”表格中，“货运保险”行的“保险服务收入”值，其他公司不用填</t>
@@ -162,21 +165,15 @@
     <t>阳光产险的“保险产品经营信息”表格中，“意外伤害和短期健康险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-保证险</t>
+    <t>保险服务收入-保证保险</t>
   </si>
   <si>
     <t>阳光产险的“保险产品经营信息”表格中，“保证险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-货物运输险</t>
-  </si>
-  <si>
     <t>阳光产险的“保险产品经营信息”表格中，“货物运输险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-责任险</t>
-  </si>
-  <si>
     <t>阳光产险的“保险产品经营信息”表格中，“责任险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
@@ -195,7 +192,7 @@
     <t>人保产险的“保险产品经营信息”表格中，“农险”行的“保险服务收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-企业财产保险</t>
+    <t>保险服务收入-企财险</t>
   </si>
   <si>
     <t>人保产险的“保险产品经营信息”表格中，“企业财产险”行的“保险服务收入”值，其他公司不用填</t>
@@ -216,15 +213,9 @@
     <t>太保财险的“保险产品经营信息”表格中，“责任险”行的“原保险保费收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-农业险</t>
-  </si>
-  <si>
     <t>太保财险的“保险产品经营信息”表格中，“农业险”行的“原保险保费收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-企财险</t>
-  </si>
-  <si>
     <t>太保财险的“保险产品经营信息”表格中，“企财险”行的“原保险保费收入”值，其他公司不用填</t>
   </si>
   <si>
@@ -270,9 +261,6 @@
     <t>众安产险的“保险产品经营信息”表格中，“家庭财产保险”行的“保费收入”值，其他公司不用填</t>
   </si>
   <si>
-    <t>保险服务收入-保证保险</t>
-  </si>
-  <si>
     <t>众安产险的“保险产品经营信息”表格中，“保证保险”行的“保费收入”值，其他公司不用填</t>
   </si>
   <si>
@@ -303,7 +291,7 @@
     <t>平安产险的“保险产品经营信息”表格中，“农业保险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-货运保险</t>
+    <t>承保利润-货物运输险</t>
   </si>
   <si>
     <t>平安产险的“保险产品经营信息”表格中，“货运保险”行的“承保利润”值，其他公司不用填</t>
@@ -321,21 +309,15 @@
     <t>阳光产险的“保险产品经营信息”表格中，“意外伤害和短期健康险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-保证险</t>
+    <t>承保利润-保证保险</t>
   </si>
   <si>
     <t>阳光产险的“保险产品经营信息”表格中，“保证险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-货物运输险</t>
-  </si>
-  <si>
     <t>阳光产险的“保险产品经营信息”表格中，“货物运输险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-责任险</t>
-  </si>
-  <si>
     <t>阳光产险的“保险产品经营信息”表格中，“责任险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
@@ -354,7 +336,7 @@
     <t>人保产险的“保险产品经营信息”表格中，“农险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-企业财产保险</t>
+    <t>承保利润-企财险</t>
   </si>
   <si>
     <t>人保产险的“保险产品经营信息”表格中，“企业财产险”行的“承保利润”值，其他公司不用填</t>
@@ -375,15 +357,9 @@
     <t>太保财险的“保险产品经营信息”表格中，“责任险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-农业险</t>
-  </si>
-  <si>
     <t>太保财险的“保险产品经营信息”表格中，“农业险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-企财险</t>
-  </si>
-  <si>
     <t>太保财险的“保险产品经营信息”表格中，“企财险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
@@ -429,9 +405,6 @@
     <t>众安产险的“保险产品经营信息”表格中，“家庭财产保险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
-    <t>承保利润-保证保险</t>
-  </si>
-  <si>
     <t>众安产险的“保险产品经营信息”表格中，“保证保险”行的“承保利润”值，其他公司不用填</t>
   </si>
   <si>
@@ -537,33 +510,39 @@
     <t>在“保险合同负债及资产”表格中，找到行中包含“保险获取现金流量的摊销”的行，取该行中“未采用保费分配法计量的合同”的合计值与“采用保费分配法计量的合同”的合计值相加。</t>
   </si>
   <si>
+    <t>维持费用（综合费用率拆解）</t>
+  </si>
+  <si>
+    <t>（[综合费用率]×[保险服务收入]）-[获取费用摊销]</t>
+  </si>
+  <si>
+    <t>综合费用率</t>
+  </si>
+  <si>
+    <t>偿付能力报告中获取</t>
+  </si>
+  <si>
+    <t>费用分类</t>
+  </si>
+  <si>
+    <t>总业务及管理费</t>
+  </si>
+  <si>
+    <t>业务及管理费表格里，小计</t>
+  </si>
+  <si>
+    <t>获取费用</t>
+  </si>
+  <si>
+    <t>业务及管理费表格里，计入未到期责任负债的保险获取现金流量</t>
+  </si>
+  <si>
     <t>维持费用</t>
   </si>
   <si>
     <t>业务及管理费表格里，计入保险服务费用的金额</t>
   </si>
   <si>
-    <t>综合费用率</t>
-  </si>
-  <si>
-    <t>([获取费用摊销]+[维持费用])/[保险服务收入]</t>
-  </si>
-  <si>
-    <t>费用分类</t>
-  </si>
-  <si>
-    <t>总业务及管理费</t>
-  </si>
-  <si>
-    <t>业务及管理费表格里，小计</t>
-  </si>
-  <si>
-    <t>获取费用</t>
-  </si>
-  <si>
-    <t>业务及管理费表格里，计入未到期责任负债的保险获取现金流量</t>
-  </si>
-  <si>
     <t>非履约费用</t>
   </si>
   <si>
@@ -637,6 +616,21 @@
   </si>
   <si>
     <t>[已发生履约现金流量变动]/[期初已发生赔款负债]</t>
+  </si>
+  <si>
+    <t>会计政策选择</t>
+  </si>
+  <si>
+    <t>折现率假设</t>
+  </si>
+  <si>
+    <t>从“折现率披露”段落中提取，格式如“1.36%至2.65%”，若为范围则写全。若未披露则留空。</t>
+  </si>
+  <si>
+    <t>非金融风险调整</t>
+  </si>
+  <si>
+    <t>从“非金融风险调整披露”段落中提取置信水平或具体数值，如“75%”或“286,451,625”。</t>
   </si>
 </sst>
 </file>
@@ -649,7 +643,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,6 +706,18 @@
     <font>
       <sz val="6.5"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1208,141 +1214,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1394,6 +1400,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1709,18 +1724,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="18.7272727272727" customWidth="1"/>
     <col min="3" max="3" width="15.7272727272727" style="2" customWidth="1"/>
     <col min="4" max="4" width="30.8181818181818" style="2" customWidth="1"/>
     <col min="5" max="5" width="9" style="2"/>
-    <col min="8" max="8" width="9" style="3"/>
-    <col min="9" max="9" width="9" style="2"/>
+    <col min="9" max="9" width="9" style="3"/>
+    <col min="10" max="10" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:9">
+    <row r="1" ht="14.5" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1742,2017 +1757,2127 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H2" s="7"/>
+      <c r="I2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H3" s="7"/>
+      <c r="I3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H4" s="7"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H5" s="7"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H6" s="7"/>
+      <c r="I6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H7" s="7"/>
+      <c r="I7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H8" s="7"/>
+      <c r="I8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A9" s="7"/>
       <c r="B9" s="14"/>
       <c r="C9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H9" s="7"/>
+      <c r="I9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A10" s="7"/>
       <c r="B10" s="14"/>
       <c r="C10" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H10" s="7"/>
+      <c r="I10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A11" s="7"/>
       <c r="B11" s="14"/>
       <c r="C11" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H11" s="7"/>
+      <c r="I11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A12" s="7"/>
       <c r="B12" s="14"/>
       <c r="C12" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H12" s="7"/>
+      <c r="I12" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A13" s="7"/>
       <c r="B13" s="14"/>
       <c r="C13" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H13" s="7"/>
+      <c r="I13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A14" s="7"/>
       <c r="B14" s="14"/>
       <c r="C14" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="I14" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H14" s="7"/>
+      <c r="J14" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A15" s="7"/>
       <c r="B15" s="14"/>
       <c r="C15" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H15" s="7"/>
+      <c r="I15" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A16" s="7"/>
       <c r="B16" s="14"/>
       <c r="C16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H16" s="7"/>
+      <c r="I16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A17" s="7"/>
       <c r="B17" s="14"/>
       <c r="C17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H17" s="7"/>
+      <c r="I17" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A18" s="7"/>
       <c r="B18" s="14"/>
       <c r="C18" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A19" s="7"/>
       <c r="B19" s="14"/>
       <c r="C19" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H19" s="7"/>
+      <c r="I19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A20" s="7"/>
       <c r="B20" s="14"/>
       <c r="C20" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H20" s="7"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A21" s="7"/>
       <c r="B21" s="14"/>
       <c r="C21" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H21" s="7"/>
+      <c r="I21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A22" s="7"/>
       <c r="B22" s="14"/>
       <c r="C22" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H22" s="7"/>
+      <c r="I22" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A23" s="7"/>
       <c r="B23" s="14"/>
       <c r="C23" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H23" s="7"/>
+      <c r="I23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A24" s="7"/>
       <c r="B24" s="14"/>
       <c r="C24" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H24" s="7"/>
+      <c r="I24" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A25" s="7"/>
       <c r="B25" s="14"/>
       <c r="C25" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H25" s="7"/>
+      <c r="I25" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A26" s="7"/>
       <c r="B26" s="14"/>
       <c r="C26" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H26" s="7"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A27" s="7"/>
       <c r="B27" s="14"/>
       <c r="C27" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H27" s="7"/>
+      <c r="I27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A28" s="7"/>
       <c r="B28" s="14"/>
       <c r="C28" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="10"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H28" s="7"/>
+      <c r="I28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A29" s="7"/>
       <c r="B29" s="14"/>
       <c r="C29" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H29" s="7"/>
+      <c r="I29" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A30" s="7"/>
       <c r="B30" s="14"/>
       <c r="C30" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H30" s="7"/>
+      <c r="I30" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A31" s="7"/>
       <c r="B31" s="14"/>
       <c r="C31" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H31" s="7"/>
+      <c r="I31" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A32" s="7"/>
       <c r="B32" s="14"/>
       <c r="C32" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H32" s="7"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A33" s="7"/>
       <c r="B33" s="14"/>
       <c r="C33" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="10"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H33" s="7"/>
+      <c r="I33" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A34" s="7"/>
       <c r="B34" s="14"/>
       <c r="C34" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" s="10"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H34" s="7"/>
+      <c r="I34" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A35" s="7"/>
       <c r="B35" s="14"/>
       <c r="C35" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I35" s="10"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H35" s="7"/>
+      <c r="I35" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A36" s="7"/>
       <c r="B36" s="14"/>
       <c r="C36" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
-      <c r="H36" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="I36" s="10"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H36" s="7"/>
+      <c r="I36" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A37" s="7"/>
       <c r="B37" s="14"/>
       <c r="C37" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
-      <c r="H37" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H37" s="7"/>
+      <c r="I37" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A38" s="7"/>
       <c r="B38" s="14"/>
       <c r="C38" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H38" s="7"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A39" s="7"/>
       <c r="B39" s="14"/>
       <c r="C39" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
-      <c r="H39" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I39" s="10"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H39" s="7"/>
+      <c r="I39" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A40" s="7"/>
       <c r="B40" s="14"/>
       <c r="C40" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" s="10"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H40" s="7"/>
+      <c r="I40" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A41" s="7"/>
       <c r="B41" s="14"/>
       <c r="C41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
-      <c r="H41" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H41" s="7"/>
+      <c r="I41" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A42" s="7"/>
       <c r="B42" s="14"/>
       <c r="C42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
-      <c r="H42" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H42" s="7"/>
+      <c r="I42" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="10"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A43" s="7"/>
       <c r="B43" s="14"/>
       <c r="C43" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="I43" s="10"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H43" s="7"/>
+      <c r="I43" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="10"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A44" s="7"/>
       <c r="B44" s="14"/>
       <c r="C44" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H44" s="7"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A45" s="7"/>
       <c r="B45" s="14"/>
       <c r="C45" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="I45" s="10"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H45" s="7"/>
+      <c r="I45" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A46" s="7"/>
       <c r="B46" s="14"/>
       <c r="C46" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="I46" s="10"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H46" s="7"/>
+      <c r="I46" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J46" s="10"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A47" s="7"/>
       <c r="B47" s="14"/>
       <c r="C47" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I47" s="10"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H47" s="7"/>
+      <c r="I47" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" s="10"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A48" s="7"/>
       <c r="B48" s="14"/>
       <c r="C48" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
-      <c r="H48" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="I48" s="10"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H48" s="7"/>
+      <c r="I48" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="J48" s="10"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A49" s="7"/>
       <c r="B49" s="14"/>
       <c r="C49" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
-      <c r="H49" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="I49" s="10"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H49" s="7"/>
+      <c r="I49" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J49" s="10"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A50" s="7"/>
       <c r="B50" s="14"/>
       <c r="C50" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H50" s="7"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A51" s="7"/>
       <c r="B51" s="14"/>
       <c r="C51" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
-      <c r="H51" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I51" s="10"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H51" s="7"/>
+      <c r="I51" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J51" s="10"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A52" s="7"/>
       <c r="B52" s="14"/>
       <c r="C52" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
-      <c r="H52" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="I52" s="10"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H52" s="7"/>
+      <c r="I52" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="J52" s="10"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A53" s="7"/>
       <c r="B53" s="14"/>
       <c r="C53" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
-      <c r="H53" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="I53" s="10"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H53" s="7"/>
+      <c r="I53" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J53" s="10"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A54" s="7"/>
       <c r="B54" s="14"/>
       <c r="C54" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="I54" s="10"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H54" s="7"/>
+      <c r="I54" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="10"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A55" s="7"/>
       <c r="B55" s="14"/>
       <c r="C55" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I55" s="10"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H55" s="7"/>
+      <c r="I55" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J55" s="10"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A56" s="7"/>
       <c r="B56" s="14"/>
       <c r="C56" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H56" s="7"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A57" s="7"/>
       <c r="B57" s="14"/>
       <c r="C57" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="I57" s="10"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H57" s="7"/>
+      <c r="I57" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A58" s="7"/>
       <c r="B58" s="14"/>
       <c r="C58" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
-      <c r="H58" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="I58" s="10"/>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H58" s="7"/>
+      <c r="I58" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A59" s="7"/>
       <c r="B59" s="14"/>
       <c r="C59" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
-      <c r="H59" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="I59" s="10"/>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H59" s="7"/>
+      <c r="I59" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" s="10"/>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A60" s="7"/>
       <c r="B60" s="14"/>
       <c r="C60" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
-      <c r="H60" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I60" s="10"/>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H60" s="7"/>
+      <c r="I60" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J60" s="10"/>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A61" s="7"/>
       <c r="B61" s="14"/>
       <c r="C61" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
-      <c r="H61" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I61" s="10"/>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H61" s="7"/>
+      <c r="I61" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J61" s="10"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A62" s="7"/>
       <c r="B62" s="14"/>
       <c r="C62" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H62" s="7"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A63" s="7"/>
       <c r="B63" s="14"/>
       <c r="C63" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
-      <c r="H63" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I63" s="10"/>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H63" s="7"/>
+      <c r="I63" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="J63" s="10"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A64" s="7"/>
       <c r="B64" s="14"/>
       <c r="C64" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
-      <c r="H64" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I64" s="10"/>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H64" s="7"/>
+      <c r="I64" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J64" s="10"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A65" s="7"/>
       <c r="B65" s="14"/>
       <c r="C65" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
-      <c r="H65" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I65" s="10"/>
-    </row>
-    <row r="66" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H65" s="7"/>
+      <c r="I65" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J65" s="10"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A66" s="7"/>
       <c r="B66" s="14"/>
       <c r="C66" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
-      <c r="H66" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="I66" s="10"/>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H66" s="7"/>
+      <c r="I66" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J66" s="10"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A67" s="7"/>
       <c r="B67" s="14"/>
       <c r="C67" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
-      <c r="H67" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="I67" s="10"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H67" s="7"/>
+      <c r="I67" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="J67" s="10"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A68" s="7"/>
       <c r="B68" s="14"/>
       <c r="C68" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H68" s="7"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A69" s="7"/>
       <c r="B69" s="14"/>
       <c r="C69" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
-      <c r="H69" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I69" s="10"/>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H69" s="7"/>
+      <c r="I69" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J69" s="10"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A70" s="7"/>
       <c r="B70" s="14"/>
       <c r="C70" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
-      <c r="H70" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="I70" s="10"/>
-    </row>
-    <row r="71" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H70" s="7"/>
+      <c r="I70" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="J70" s="10"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A71" s="7"/>
       <c r="B71" s="14"/>
       <c r="C71" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
-      <c r="H71" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="I71" s="10"/>
-    </row>
-    <row r="72" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H71" s="7"/>
+      <c r="I71" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="J71" s="10"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A72" s="7"/>
       <c r="B72" s="14"/>
       <c r="C72" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
-      <c r="H72" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I72" s="10"/>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H72" s="7"/>
+      <c r="I72" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="J72" s="10"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A73" s="7"/>
       <c r="B73" s="14"/>
       <c r="C73" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
-      <c r="H73" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="I73" s="10"/>
-    </row>
-    <row r="74" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H73" s="7"/>
+      <c r="I73" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="J73" s="10"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A74" s="7"/>
       <c r="B74" s="14"/>
       <c r="C74" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H74" s="7"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A75" s="7"/>
       <c r="B75" s="14"/>
       <c r="C75" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
-      <c r="H75" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I75" s="10"/>
-    </row>
-    <row r="76" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H75" s="7"/>
+      <c r="I75" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J75" s="10"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A76" s="7"/>
       <c r="B76" s="14"/>
       <c r="C76" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
-      <c r="H76" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="I76" s="10"/>
-    </row>
-    <row r="77" s="1" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H76" s="7"/>
+      <c r="I76" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="J76" s="10"/>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="14.5" spans="1:10">
       <c r="A77" s="7"/>
       <c r="B77" s="14"/>
       <c r="C77" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
-      <c r="H77" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I77" s="10"/>
-    </row>
-    <row r="78" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H77" s="7"/>
+      <c r="I77" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J77" s="10"/>
+    </row>
+    <row r="78" customFormat="1" ht="14.5" spans="1:10">
       <c r="C78" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
-      <c r="H78" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="I78" s="10"/>
-    </row>
-    <row r="79" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H78" s="7"/>
+      <c r="I78" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="J78" s="10"/>
+    </row>
+    <row r="79" customFormat="1" ht="14.5" spans="1:10">
       <c r="C79" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
-      <c r="H79" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I79" s="10"/>
-    </row>
-    <row r="80" customFormat="1" ht="14.5" spans="1:9">
+      <c r="H79" s="7"/>
+      <c r="I79" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="J79" s="10"/>
+    </row>
+    <row r="80" customFormat="1" ht="14.5" spans="1:10">
       <c r="C80" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="16" t="s">
+      <c r="H80" s="7"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10">
+      <c r="C81" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="82" spans="3:10">
+      <c r="C82" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="3:10">
+      <c r="C83" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10">
+      <c r="C84" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10">
+      <c r="C85" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="81" spans="3:9">
-      <c r="C81" s="2" t="s">
+      <c r="E85" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D81" s="2" t="s">
+    </row>
+    <row r="86" spans="3:10">
+      <c r="C86" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="17" t="s">
+      <c r="E86" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="3:9">
-      <c r="C82" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" s="2" t="s">
+    <row r="87" spans="3:10">
+      <c r="C87" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="3:9">
-      <c r="C83" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="9" t="s">
+      <c r="E87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10">
+      <c r="C88" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="84" spans="3:9">
-      <c r="C84" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D84" s="2" t="s">
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10">
+      <c r="C89" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E84" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="9"/>
-      <c r="I84" s="2" t="s">
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10">
+      <c r="C90" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="3:9">
-      <c r="C85" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D85" s="2" t="s">
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10">
+      <c r="C91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E85" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H85" s="9"/>
-      <c r="I85" s="2" t="s">
+      <c r="E91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10">
+      <c r="C92" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="86" spans="3:9">
-      <c r="C86" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="E92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="3:10">
+      <c r="C93" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E86" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H86" s="9"/>
-      <c r="I86" s="2" t="s">
+    </row>
+    <row r="94" spans="3:10">
+      <c r="C94" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="87" spans="3:9">
-      <c r="C87" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="E94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="3:9">
-      <c r="C88" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D88" s="2" t="s">
+    </row>
+    <row r="95" spans="3:10">
+      <c r="C95" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="3:9">
-      <c r="C89" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D89" s="2" t="s">
+      <c r="E95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90" spans="3:9">
-      <c r="C90" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D90" s="2" t="s">
+    </row>
+    <row r="96" spans="3:10">
+      <c r="C96" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="3:9">
-      <c r="C91" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D91" s="2" t="s">
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="3:9">
-      <c r="C92" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D92" s="2" t="s">
+    </row>
+    <row r="97" spans="3:10">
+      <c r="C97" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="3:9">
-      <c r="C93" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" s="2" t="s">
+      <c r="E97" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" s="17"/>
+      <c r="J97" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="3:9">
-      <c r="C94" s="2" t="s">
+    <row r="98" spans="3:10">
+      <c r="C98" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E98" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="17"/>
+      <c r="J98" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H94" s="18" t="s">
+    </row>
+    <row r="99" spans="3:10">
+      <c r="C99" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="95" spans="3:9">
-      <c r="C95" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H95" s="17" t="s">
+    </row>
+    <row r="100" spans="3:10">
+      <c r="C100" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D100" s="19" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="96" spans="3:9">
-      <c r="C96" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D96" s="2" t="s">
+      <c r="E100" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="17"/>
+      <c r="J100" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="17" t="s">
+    </row>
+    <row r="101" spans="3:10">
+      <c r="C101" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="97" spans="3:9">
-      <c r="C97" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D97" s="2" t="s">
+      <c r="E101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="E97" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H97" s="17"/>
-      <c r="I97" s="2" t="s">
+    </row>
+    <row r="102" spans="3:10">
+      <c r="C102" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="98" spans="3:9">
-      <c r="C98" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D98" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E98" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H98" s="17"/>
-      <c r="I98" s="2" t="s">
+      <c r="E102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" s="17" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="99" spans="3:9">
-      <c r="C99" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D99" s="2" t="s">
+    <row r="103" spans="3:10">
+      <c r="C103" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H99" s="17" t="s">
+      <c r="E103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" s="17" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:9">
-      <c r="C100" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="101" spans="3:9">
-      <c r="C101" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H101" s="17"/>
-      <c r="I101" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="102" spans="3:9">
-      <c r="C102" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H102" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="103" spans="3:9">
-      <c r="C103" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" s="17" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="104" spans="3:9">
+    <row r="104" spans="3:10">
       <c r="C104" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>166</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H104" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" s="17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="105" spans="3:9">
+    <row r="105" spans="3:10">
       <c r="C105" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10">
+      <c r="C106" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="E106" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10">
+      <c r="C107" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="108" spans="3:10">
+      <c r="C108" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H105" s="17" t="s">
+      <c r="E108" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="17"/>
+      <c r="J108" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="106" spans="3:9">
-      <c r="C106" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D106" s="2" t="s">
+    <row r="109" spans="3:10">
+      <c r="C109" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E106" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H106" s="17" t="s">
+      <c r="E109" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="J109" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="107" spans="3:9">
-      <c r="C107" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D107" s="2" t="s">
+    <row r="110" spans="3:10">
+      <c r="C110" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E107" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H107" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="I107" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="108" spans="3:9">
-      <c r="C108" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D108" s="2" t="s">
+      <c r="E110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E108" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H108" s="17"/>
-      <c r="I108" s="2" t="s">
+    </row>
+    <row r="111" spans="3:10">
+      <c r="C111" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="109" spans="3:9">
-      <c r="C109" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D109" s="2" t="s">
+      <c r="E111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="E109" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H109" s="17" t="s">
+    </row>
+    <row r="112" spans="3:10">
+      <c r="C112" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I109" s="2" t="s">
+      <c r="E112" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="17"/>
+      <c r="J112" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="110" spans="3:9">
-      <c r="C110" s="2" t="s">
+    <row r="113" spans="3:10">
+      <c r="C113" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="E113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H110" s="17" t="s">
+    </row>
+    <row r="114" spans="3:10">
+      <c r="C114" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="111" spans="3:9">
-      <c r="C111" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D111" s="2" t="s">
+      <c r="E114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H111" s="17" t="s">
+    </row>
+    <row r="115" spans="3:10">
+      <c r="C115" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="112" spans="3:9">
-      <c r="C112" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D112" s="2" t="s">
+      <c r="E115" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="17"/>
+      <c r="J115" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E112" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H112" s="17"/>
-      <c r="I112" s="2" t="s">
+    </row>
+    <row r="116" ht="14.5" spans="3:10">
+      <c r="C116" s="21" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="113" spans="3:9">
-      <c r="C113" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D113" s="2" t="s">
+      <c r="D116" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H113" s="17" t="s">
+      <c r="E116" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" s="17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="114" spans="3:9">
-      <c r="C114" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D114" s="2" t="s">
+    <row r="117" ht="14.5" spans="3:10">
+      <c r="C117" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D117" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H114" s="17" t="s">
+      <c r="E117" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" s="17" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="115" spans="3:9">
-      <c r="C115" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H115" s="17"/>
-      <c r="I115" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:G121" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:H121" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
